--- a/automation/reports/excel/Failed_Test_Cases.xlsx
+++ b/automation/reports/excel/Failed_Test_Cases.xlsx
@@ -397,91 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Test ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Module</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Test Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Error Message</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Execution Time (ms)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>TC_FORM_025</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Forms</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Form Inputs and Submission Scenario #25</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Assertion Error: Input validation pattern failed to trigger warning toast.</v>
-      </c>
-      <c r="F2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>TC_VAL_012</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Input Validation</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Input Pattern Checks Scenario #12</v>
-      </c>
-      <c r="D3" t="str">
-        <v>High</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Assertion Error: Input validation pattern failed to trigger warning toast.</v>
-      </c>
-      <c r="F3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>TC_FILE_002</v>
-      </c>
-      <c r="B4" t="str">
-        <v>File Upload</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Upload Profile Image Scenario #2</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Low</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Assertion Error: Input validation pattern failed to trigger warning toast.</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>